--- a/data/trans_orig/P23_1_2016_2023_R2-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P23_1_2016_2023_R2-Estudios-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no fuma pero ha fumado (prevalencia exfumadores) en 2016</t>
+          <t>Población que no fuma pero ha fumado (prevalencia exfumadores) en 2016 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>215453</t>
+          <t>217320</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>265417</t>
+          <t>266856</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>36699</t>
+          <t>35961</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>64840</t>
+          <t>64097</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>260231</t>
+          <t>260621</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>321536</t>
+          <t>320432</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,35%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>488065</t>
+          <t>486626</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>538029</t>
+          <t>536162</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>64,77%</t>
+          <t>64,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>71,41%</t>
+          <t>71,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>927426</t>
+          <t>928169</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>955567</t>
+          <t>956305</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1424212</t>
+          <t>1425316</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1485517</t>
+          <t>1485127</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>81,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>85,07%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>324046</t>
+          <t>322922</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>394655</t>
+          <t>392545</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>204093</t>
+          <t>202647</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>265709</t>
+          <t>262482</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>547926</t>
+          <t>543171</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>640196</t>
+          <t>638669</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,72%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1681730</t>
+          <t>1683840</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1752339</t>
+          <t>1753463</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,39%</t>
+          <t>84,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1720475</t>
+          <t>1723702</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1782091</t>
+          <t>1783537</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>86,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3422372</t>
+          <t>3423899</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3514642</t>
+          <t>3519397</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>84,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>86,63%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>84072</t>
+          <t>81781</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>121454</t>
+          <t>121551</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>84734</t>
+          <t>85840</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>124410</t>
+          <t>125316</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>176563</t>
+          <t>179473</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>230561</t>
+          <t>232846</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,28%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>424360</t>
+          <t>424263</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>461742</t>
+          <t>464033</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,75%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>85,02%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>423803</t>
+          <t>422897</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>463479</t>
+          <t>462373</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>77,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>84,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>863466</t>
+          <t>861181</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>917464</t>
+          <t>914554</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,93%</t>
+          <t>78,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,86%</t>
+          <t>83,6%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>652949</t>
+          <t>650518</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>749727</t>
+          <t>750855</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>347254</t>
+          <t>349829</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>425013</t>
+          <t>428037</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1026810</t>
+          <t>1022427</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1145799</t>
+          <t>1147266</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,62%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2625954</t>
+          <t>2624826</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2722732</t>
+          <t>2725163</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,79%</t>
+          <t>77,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,66%</t>
+          <t>80,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3101649</t>
+          <t>3098625</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3179408</t>
+          <t>3176833</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>87,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5756544</t>
+          <t>5755077</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5875533</t>
+          <t>5879916</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,4%</t>
+          <t>83,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>85,19%</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no fuma pero ha fumado (prevalencia exfumadores) en 2023</t>
+          <t>Población que no fuma pero ha fumado (prevalencia exfumadores) en 2023 (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2334,12 +2334,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>148656</t>
+          <t>148895</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>187891</t>
+          <t>184772</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2349,12 +2349,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>35,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2369,12 +2369,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>35483</t>
+          <t>35260</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>56068</t>
+          <t>56434</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2404,12 +2404,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>188552</t>
+          <t>188856</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>233449</t>
+          <t>235246</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2419,12 +2419,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,52%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>327047</t>
+          <t>330166</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>366282</t>
+          <t>366043</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>63,51%</t>
+          <t>64,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>71,13%</t>
+          <t>71,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>699440</t>
+          <t>699074</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>720025</t>
+          <t>720248</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1036997</t>
+          <t>1035200</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1081894</t>
+          <t>1081590</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,62%</t>
+          <t>81,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>85,13%</t>
         </is>
       </c>
     </row>
@@ -2677,12 +2677,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>324631</t>
+          <t>324738</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1079570</t>
+          <t>981371</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>47,18%</t>
+          <t>42,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2712,12 +2712,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>146799</t>
+          <t>157962</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>240247</t>
+          <t>242287</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2727,12 +2727,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2747,12 +2747,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>507394</t>
+          <t>502168</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1419786</t>
+          <t>1425195</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2762,12 +2762,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,5%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1208724</t>
+          <t>1306923</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1963663</t>
+          <t>1963556</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2805,7 +2805,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>52,82%</t>
+          <t>57,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1996232</t>
+          <t>1994192</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2089680</t>
+          <t>2078517</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3104988</t>
+          <t>3099579</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4017380</t>
+          <t>4022606</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,62%</t>
+          <t>68,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>88,9%</t>
         </is>
       </c>
     </row>
@@ -3020,12 +3020,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>119177</t>
+          <t>118254</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>163190</t>
+          <t>161052</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3035,12 +3035,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>73528</t>
+          <t>72860</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>103647</t>
+          <t>102372</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3070,12 +3070,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>201128</t>
+          <t>202373</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>251239</t>
+          <t>251506</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3105,12 +3105,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,28%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>483433</t>
+          <t>485571</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>527446</t>
+          <t>528369</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,76%</t>
+          <t>75,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>81,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>554254</t>
+          <t>555529</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>584373</t>
+          <t>585041</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>84,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1053286</t>
+          <t>1053019</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1103397</t>
+          <t>1102152</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>80,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,58%</t>
+          <t>84,49%</t>
         </is>
       </c>
     </row>
@@ -3363,12 +3363,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>635396</t>
+          <t>639367</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1414674</t>
+          <t>1478840</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3378,12 +3378,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>278900</t>
+          <t>278125</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>375939</t>
+          <t>375943</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3413,7 +3413,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>940672</t>
+          <t>946471</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1944120</t>
+          <t>1852348</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3448,12 +3448,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>26,09%</t>
         </is>
       </c>
     </row>
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2035182</t>
+          <t>1971016</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2814460</t>
+          <t>2810489</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,99%</t>
+          <t>57,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>81,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3273949</t>
+          <t>3273945</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3370988</t>
+          <t>3371763</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5155625</t>
+          <t>5247397</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6159073</t>
+          <t>6153274</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>73,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>86,67%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P23_1_2016_2023_R2-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P23_1_2016_2023_R2-Estudios-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>217320</t>
+          <t>217415</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>266856</t>
+          <t>266229</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>35,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>35961</t>
+          <t>35416</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>64097</t>
+          <t>62230</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>260621</t>
+          <t>259567</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>320432</t>
+          <t>319568</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,31%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>486626</t>
+          <t>487253</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>536162</t>
+          <t>536067</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>64,58%</t>
+          <t>64,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>71,16%</t>
+          <t>71,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>928169</t>
+          <t>930036</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>956305</t>
+          <t>956850</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1425316</t>
+          <t>1426180</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1485127</t>
+          <t>1486181</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,65%</t>
+          <t>81,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>85,13%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>322922</t>
+          <t>322542</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>392545</t>
+          <t>393381</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>202647</t>
+          <t>205177</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>262482</t>
+          <t>260051</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>543171</t>
+          <t>545689</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>638669</t>
+          <t>636324</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,66%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1683840</t>
+          <t>1683004</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1753463</t>
+          <t>1753843</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,09%</t>
+          <t>81,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1723702</t>
+          <t>1726133</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1783537</t>
+          <t>1781007</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>86,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3423899</t>
+          <t>3426244</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3519397</t>
+          <t>3516879</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>84,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>86,57%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>81781</t>
+          <t>83569</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>121551</t>
+          <t>122058</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>85840</t>
+          <t>87947</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>125316</t>
+          <t>126586</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>179473</t>
+          <t>178053</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>232846</t>
+          <t>230873</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,1%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>424263</t>
+          <t>423756</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>464033</t>
+          <t>462245</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>77,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>84,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>422897</t>
+          <t>421627</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>462373</t>
+          <t>460266</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,14%</t>
+          <t>76,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,34%</t>
+          <t>83,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>861181</t>
+          <t>863154</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>914554</t>
+          <t>915974</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,72%</t>
+          <t>78,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>83,73%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>650518</t>
+          <t>650448</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>750855</t>
+          <t>746644</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>349829</t>
+          <t>348857</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>428037</t>
+          <t>426510</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1022427</t>
+          <t>1024598</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1147266</t>
+          <t>1147161</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2624826</t>
+          <t>2629037</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2725163</t>
+          <t>2725233</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,76%</t>
+          <t>77,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3098625</t>
+          <t>3100152</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3176833</t>
+          <t>3177805</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5755077</t>
+          <t>5755182</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5879916</t>
+          <t>5877745</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1963,7 +1963,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>85,16%</t>
         </is>
       </c>
     </row>
@@ -2329,32 +2329,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>166717</t>
+          <t>177221</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>148895</t>
+          <t>156002</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>184772</t>
+          <t>198340</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>34,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2364,32 +2364,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>44933</t>
+          <t>47704</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>35260</t>
+          <t>38037</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>56434</t>
+          <t>60491</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2399,32 +2399,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>211650</t>
+          <t>224925</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>188856</t>
+          <t>200931</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>235246</t>
+          <t>250524</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>17,89%</t>
         </is>
       </c>
     </row>
@@ -2442,32 +2442,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>348221</t>
+          <t>401308</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>330166</t>
+          <t>380189</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>366043</t>
+          <t>422527</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>67,62%</t>
+          <t>69,37%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>64,12%</t>
+          <t>65,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>71,08%</t>
+          <t>73,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2477,32 +2477,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>710575</t>
+          <t>774334</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>699074</t>
+          <t>761547</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>720248</t>
+          <t>784001</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2512,32 +2512,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1058796</t>
+          <t>1175642</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1035200</t>
+          <t>1150043</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1081590</t>
+          <t>1199636</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,48%</t>
+          <t>82,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>85,65%</t>
         </is>
       </c>
     </row>
@@ -2555,17 +2555,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2590,17 +2590,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2625,17 +2625,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -2672,32 +2672,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>545224</t>
+          <t>333396</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>324738</t>
+          <t>300399</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>981371</t>
+          <t>366096</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2707,32 +2707,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>203124</t>
+          <t>222123</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>157962</t>
+          <t>197738</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>242287</t>
+          <t>246998</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2742,32 +2742,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>748348</t>
+          <t>555519</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>502168</t>
+          <t>510898</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1425195</t>
+          <t>596085</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>13,55%</t>
         </is>
       </c>
     </row>
@@ -2785,32 +2785,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1743070</t>
+          <t>1894947</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1306923</t>
+          <t>1862247</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1963556</t>
+          <t>1927944</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>76,17%</t>
+          <t>85,04%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>57,11%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,81%</t>
+          <t>86,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2820,32 +2820,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2033355</t>
+          <t>1947861</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1994192</t>
+          <t>1922986</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2078517</t>
+          <t>1972246</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,17%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2855,32 +2855,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>3776426</t>
+          <t>3842808</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3099579</t>
+          <t>3802242</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4022606</t>
+          <t>3887429</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,5%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>88,38%</t>
         </is>
       </c>
     </row>
@@ -2898,17 +2898,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2288294</t>
+          <t>2228343</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2288294</t>
+          <t>2228343</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2288294</t>
+          <t>2228343</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2933,17 +2933,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2236479</t>
+          <t>2169984</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2236479</t>
+          <t>2169984</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2236479</t>
+          <t>2169984</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -2968,17 +2968,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4524774</t>
+          <t>4398327</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4524774</t>
+          <t>4398327</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4524774</t>
+          <t>4398327</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3015,32 +3015,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>138425</t>
+          <t>149869</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>118254</t>
+          <t>129120</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>161052</t>
+          <t>174023</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3050,32 +3050,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>87092</t>
+          <t>95589</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>72860</t>
+          <t>81526</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>102372</t>
+          <t>113049</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3085,32 +3085,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>225517</t>
+          <t>245458</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>202373</t>
+          <t>222141</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>251506</t>
+          <t>273753</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>18,96%</t>
         </is>
       </c>
     </row>
@@ -3128,32 +3128,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>508198</t>
+          <t>561718</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>485571</t>
+          <t>537564</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>528369</t>
+          <t>582467</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>78,59%</t>
+          <t>78,94%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>75,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,71%</t>
+          <t>81,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3163,32 +3163,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>570809</t>
+          <t>636825</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>555529</t>
+          <t>619365</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>585041</t>
+          <t>650888</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>84,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3198,32 +3198,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1079008</t>
+          <t>1198543</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1053019</t>
+          <t>1170248</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1102152</t>
+          <t>1221860</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>83,0%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,72%</t>
+          <t>81,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>84,62%</t>
         </is>
       </c>
     </row>
@@ -3241,17 +3241,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3276,17 +3276,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>657901</t>
+          <t>732414</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>657901</t>
+          <t>732414</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>657901</t>
+          <t>732414</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3311,17 +3311,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1304525</t>
+          <t>1444001</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1304525</t>
+          <t>1444001</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1304525</t>
+          <t>1444001</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3358,32 +3358,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>850366</t>
+          <t>660485</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>639367</t>
+          <t>612617</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1478840</t>
+          <t>710516</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,87%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3393,32 +3393,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>335149</t>
+          <t>365417</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>278125</t>
+          <t>332989</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>375943</t>
+          <t>400495</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3428,32 +3428,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1185515</t>
+          <t>1025902</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>946471</t>
+          <t>974580</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1852348</t>
+          <t>1085832</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>14,99%</t>
         </is>
       </c>
     </row>
@@ -3471,32 +3471,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2599490</t>
+          <t>2857974</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1971016</t>
+          <t>2807943</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2810489</t>
+          <t>2905842</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>81,23%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>57,13%</t>
+          <t>79,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,47%</t>
+          <t>82,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3314739</t>
+          <t>3359018</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3273945</t>
+          <t>3323940</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3371763</t>
+          <t>3391446</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>5914230</t>
+          <t>6216993</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5247397</t>
+          <t>6157063</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6153274</t>
+          <t>6268315</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>85,84%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,91%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,67%</t>
+          <t>86,54%</t>
         </is>
       </c>
     </row>
@@ -3584,17 +3584,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3449856</t>
+          <t>3518459</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3449856</t>
+          <t>3518459</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3449856</t>
+          <t>3518459</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -3619,17 +3619,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3649888</t>
+          <t>3724435</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3649888</t>
+          <t>3724435</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3649888</t>
+          <t>3724435</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3654,17 +3654,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7099745</t>
+          <t>7242895</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7099745</t>
+          <t>7242895</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7099745</t>
+          <t>7242895</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
